--- a/data/derived_data/3_CommunityComposition/Dataset_2/ps_rare_ITS_Dataset_2_mtd_table.xlsx
+++ b/data/derived_data/3_CommunityComposition/Dataset_2/ps_rare_ITS_Dataset_2_mtd_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t xml:space="preserve">MS_183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_184</t>
   </si>
   <si>
     <t xml:space="preserve">MS_185</t>
@@ -5106,7 +5109,7 @@
         <v>153</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C73" t="s">
         <v>60</v>
@@ -5133,13 +5136,13 @@
         <v>52</v>
       </c>
       <c r="K73" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="L73" t="s">
         <v>101</v>
       </c>
       <c r="M73" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="N73" t="s">
         <v>32</v>
@@ -5148,7 +5151,7 @@
         <v>26</v>
       </c>
       <c r="P73" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Q73" t="s">
         <v>26</v>
@@ -5165,7 +5168,7 @@
         <v>154</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C74" t="s">
         <v>60</v>
@@ -5224,7 +5227,7 @@
         <v>155</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C75" t="s">
         <v>60</v>
@@ -5251,13 +5254,13 @@
         <v>52</v>
       </c>
       <c r="K75" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="L75" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="M75" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="N75" t="s">
         <v>32</v>
@@ -5266,7 +5269,7 @@
         <v>26</v>
       </c>
       <c r="P75" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="Q75" t="s">
         <v>26</v>
@@ -5283,7 +5286,7 @@
         <v>156</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C76" t="s">
         <v>60</v>
@@ -5342,7 +5345,7 @@
         <v>157</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
         <v>60</v>
@@ -5366,16 +5369,16 @@
         <v>27</v>
       </c>
       <c r="J77" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="K77" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="L77" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="M77" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="N77" t="s">
         <v>32</v>
@@ -5401,7 +5404,7 @@
         <v>158</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C78" t="s">
         <v>60</v>
@@ -5460,13 +5463,13 @@
         <v>159</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C79" t="s">
         <v>60</v>
       </c>
       <c r="D79" t="s">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="E79" t="s">
         <v>23</v>
@@ -5484,25 +5487,25 @@
         <v>27</v>
       </c>
       <c r="J79" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K79" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="L79" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="M79" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="N79" t="s">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="O79" t="s">
         <v>26</v>
       </c>
       <c r="P79" t="s">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="Q79" t="s">
         <v>26</v>
@@ -5516,10 +5519,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B80" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C80" t="s">
         <v>60</v>
@@ -5561,16 +5564,16 @@
         <v>26</v>
       </c>
       <c r="P80" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>26</v>
+      </c>
+      <c r="R80" t="s">
+        <v>34</v>
+      </c>
+      <c r="S80" t="s">
         <v>160</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>26</v>
-      </c>
-      <c r="R80" t="s">
-        <v>34</v>
-      </c>
-      <c r="S80" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="81">
@@ -5578,7 +5581,7 @@
         <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C81" t="s">
         <v>60</v>
@@ -5605,13 +5608,13 @@
         <v>43</v>
       </c>
       <c r="K81" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L81" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="M81" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="N81" t="s">
         <v>145</v>
@@ -5620,7 +5623,7 @@
         <v>26</v>
       </c>
       <c r="P81" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="Q81" t="s">
         <v>26</v>
@@ -5637,7 +5640,7 @@
         <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C82" t="s">
         <v>60</v>
@@ -5705,7 +5708,7 @@
         <v>144</v>
       </c>
       <c r="E83" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F83" t="s">
         <v>141</v>
@@ -5723,13 +5726,13 @@
         <v>43</v>
       </c>
       <c r="K83" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="L83" t="s">
         <v>92</v>
       </c>
       <c r="M83" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="N83" t="s">
         <v>145</v>
@@ -5738,7 +5741,7 @@
         <v>26</v>
       </c>
       <c r="P83" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="Q83" t="s">
         <v>26</v>
@@ -5755,7 +5758,7 @@
         <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C84" t="s">
         <v>60</v>
@@ -5764,7 +5767,7 @@
         <v>144</v>
       </c>
       <c r="E84" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F84" t="s">
         <v>141</v>
@@ -5779,16 +5782,16 @@
         <v>27</v>
       </c>
       <c r="J84" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="K84" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="L84" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="M84" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="N84" t="s">
         <v>145</v>
@@ -5797,7 +5800,7 @@
         <v>26</v>
       </c>
       <c r="P84" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q84" t="s">
         <v>26</v>
@@ -5814,7 +5817,7 @@
         <v>166</v>
       </c>
       <c r="B85" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C85" t="s">
         <v>60</v>
@@ -5856,7 +5859,7 @@
         <v>26</v>
       </c>
       <c r="P85" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q85" t="s">
         <v>26</v>
@@ -5873,7 +5876,7 @@
         <v>167</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C86" t="s">
         <v>60</v>
@@ -5900,13 +5903,13 @@
         <v>52</v>
       </c>
       <c r="K86" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="L86" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="M86" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="N86" t="s">
         <v>145</v>
@@ -5915,7 +5918,7 @@
         <v>26</v>
       </c>
       <c r="P86" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="Q86" t="s">
         <v>26</v>
@@ -5932,7 +5935,7 @@
         <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C87" t="s">
         <v>60</v>
@@ -5991,7 +5994,7 @@
         <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C88" t="s">
         <v>60</v>
@@ -6000,7 +6003,7 @@
         <v>144</v>
       </c>
       <c r="E88" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F88" t="s">
         <v>141</v>
@@ -6018,13 +6021,13 @@
         <v>52</v>
       </c>
       <c r="K88" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="L88" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="M88" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="N88" t="s">
         <v>145</v>
@@ -6050,7 +6053,7 @@
         <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C89" t="s">
         <v>60</v>
@@ -6102,6 +6105,65 @@
       </c>
       <c r="S89" t="s">
         <v>170</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" t="s">
+        <v>60</v>
+      </c>
+      <c r="D90" t="s">
+        <v>144</v>
+      </c>
+      <c r="E90" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90" t="s">
+        <v>141</v>
+      </c>
+      <c r="G90" t="s">
+        <v>25</v>
+      </c>
+      <c r="H90" t="s">
+        <v>26</v>
+      </c>
+      <c r="I90" t="s">
+        <v>27</v>
+      </c>
+      <c r="J90" t="s">
+        <v>52</v>
+      </c>
+      <c r="K90" t="s">
+        <v>100</v>
+      </c>
+      <c r="L90" t="s">
+        <v>101</v>
+      </c>
+      <c r="M90" t="s">
+        <v>102</v>
+      </c>
+      <c r="N90" t="s">
+        <v>145</v>
+      </c>
+      <c r="O90" t="s">
+        <v>26</v>
+      </c>
+      <c r="P90" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>26</v>
+      </c>
+      <c r="R90" t="s">
+        <v>34</v>
+      </c>
+      <c r="S90" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
